--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -98,7 +98,10 @@
     <t>Dungeon42-1</t>
   </si>
   <si>
-    <t>Dungeon52-1</t>
+    <t>Dungeon50-1</t>
+  </si>
+  <si>
+    <t>Dungeon50-2</t>
   </si>
   <si>
     <t>Actor0001_1</t>
@@ -281,14 +284,52 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -302,9 +343,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,91 +380,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -424,8 +397,38 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,7 +450,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,7 +516,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,19 +588,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,115 +612,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -621,13 +630,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,21 +641,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -672,16 +660,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -689,8 +677,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -706,8 +694,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -730,11 +720,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,145 +749,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1211,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1764,9 +1767,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
-        <v>10110</v>
+        <v>1070</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1790,9 +1793,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:8">
+    <row r="23" spans="1:8">
       <c r="A23">
-        <v>10120</v>
+        <v>10110</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1818,7 +1821,7 @@
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1844,7 +1847,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>10210</v>
+        <v>10130</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1870,7 +1873,7 @@
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10220</v>
+        <v>10210</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1922,7 +1925,7 @@
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>10310</v>
+        <v>10230</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1948,7 +1951,7 @@
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10320</v>
+        <v>10310</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1974,7 +1977,7 @@
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10330</v>
+        <v>10320</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -2000,7 +2003,7 @@
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10410</v>
+        <v>10330</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2026,7 +2029,7 @@
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10420</v>
+        <v>10410</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
@@ -2052,7 +2055,7 @@
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10430</v>
+        <v>10420</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -2078,7 +2081,7 @@
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10510</v>
+        <v>10430</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2104,7 +2107,7 @@
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10520</v>
+        <v>10510</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2130,7 +2133,7 @@
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10530</v>
+        <v>10520</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
@@ -2156,7 +2159,7 @@
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10610</v>
+        <v>10530</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2182,7 +2185,7 @@
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>10620</v>
+        <v>10610</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
@@ -2208,7 +2211,7 @@
     </row>
     <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>10630</v>
+        <v>10620</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -2234,7 +2237,7 @@
     </row>
     <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
-        <v>10710</v>
+        <v>10630</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2260,7 +2263,7 @@
     </row>
     <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
-        <v>10720</v>
+        <v>10710</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -2286,7 +2289,7 @@
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
-        <v>10730</v>
+        <v>10720</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
@@ -2312,7 +2315,7 @@
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
-        <v>10810</v>
+        <v>10730</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -2338,7 +2341,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
-        <v>10820</v>
+        <v>10810</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -2364,7 +2367,7 @@
     </row>
     <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
-        <v>10830</v>
+        <v>10820</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -2390,7 +2393,7 @@
     </row>
     <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
-        <v>10910</v>
+        <v>10830</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
@@ -2416,7 +2419,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
-        <v>10920</v>
+        <v>10910</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -2442,7 +2445,7 @@
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
-        <v>10930</v>
+        <v>10920</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2468,7 +2471,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
-        <v>11010</v>
+        <v>10930</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -2494,7 +2497,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
@@ -2520,7 +2523,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:8">
       <c r="A51">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2546,7 +2549,7 @@
     </row>
     <row r="52" customFormat="1" spans="1:8">
       <c r="A52">
-        <v>12010</v>
+        <v>11030</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2572,7 +2575,7 @@
     </row>
     <row r="53" customFormat="1" spans="1:8">
       <c r="A53">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
@@ -2598,7 +2601,7 @@
     </row>
     <row r="54" customFormat="1" spans="1:8">
       <c r="A54">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B54" t="s">
         <v>60</v>
@@ -2622,9 +2625,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" customFormat="1" spans="1:8">
       <c r="A55">
-        <v>20010</v>
+        <v>12030</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
@@ -2648,9 +2651,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" customFormat="1" spans="1:8">
+    <row r="56" spans="1:8">
       <c r="A56">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -2674,9 +2677,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" customFormat="1" spans="1:8">
       <c r="A57">
-        <v>30010</v>
+        <v>20020</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
@@ -2685,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2700,9 +2703,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="1" spans="1:8">
+    <row r="58" spans="1:8">
       <c r="A58">
-        <v>30011</v>
+        <v>30010</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
@@ -2711,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2726,9 +2729,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" customFormat="1" spans="1:8">
       <c r="A59">
-        <v>30020</v>
+        <v>30011</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B60" t="s">
         <v>66</v>
@@ -2780,7 +2783,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -2806,7 +2809,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>30050</v>
+        <v>30040</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
@@ -2832,7 +2835,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>30060</v>
+        <v>30050</v>
       </c>
       <c r="B63" t="s">
         <v>69</v>
@@ -2858,7 +2861,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>30110</v>
+        <v>30060</v>
       </c>
       <c r="B64" t="s">
         <v>70</v>
@@ -2867,18 +2870,44 @@
         <v>0</v>
       </c>
       <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>30110</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
         <v>2010</v>
       </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64" t="b">
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2896,7 +2925,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2904,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2912,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2920,7 +2949,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2928,7 +2957,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2936,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2944,7 +2973,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2952,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2960,7 +2989,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2968,7 +2997,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2976,7 +3005,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2984,7 +3013,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2992,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3000,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3008,7 +3037,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Interrude4-2</t>
+  </si>
+  <si>
+    <t>Interrude5-1</t>
+  </si>
+  <si>
+    <t>Interrude5-2</t>
   </si>
   <si>
     <t>Encount</t>
@@ -284,9 +290,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -298,15 +304,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,70 +326,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,23 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -435,11 +364,88 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -447,6 +453,144 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -456,37 +600,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,139 +624,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,21 +647,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -670,35 +661,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -718,15 +680,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -741,6 +694,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -749,145 +755,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1214,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1457,7 +1463,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:8">
       <c r="A10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -1483,7 +1489,7 @@
     </row>
     <row r="11" customFormat="1" spans="1:8">
       <c r="A11">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -1509,7 +1515,7 @@
     </row>
     <row r="12" customFormat="1" spans="1:8">
       <c r="A12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
@@ -1535,7 +1541,7 @@
     </row>
     <row r="13" customFormat="1" spans="1:8">
       <c r="A13">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -1561,7 +1567,7 @@
     </row>
     <row r="14" customFormat="1" spans="1:8">
       <c r="A14">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
@@ -1587,7 +1593,7 @@
     </row>
     <row r="15" customFormat="1" spans="1:8">
       <c r="A15">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
@@ -1613,7 +1619,7 @@
     </row>
     <row r="16" customFormat="1" spans="1:8">
       <c r="A16">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1639,7 +1645,7 @@
     </row>
     <row r="17" customFormat="1" spans="1:8">
       <c r="A17">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -1663,9 +1669,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" customFormat="1" spans="1:8">
       <c r="A18">
-        <v>1030</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1691,7 +1697,7 @@
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
-        <v>1040</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
@@ -1715,9 +1721,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:8">
+    <row r="20" spans="1:8">
       <c r="A20">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1743,7 +1749,7 @@
     </row>
     <row r="21" customFormat="1" spans="1:8">
       <c r="A21">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -1769,7 +1775,7 @@
     </row>
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1793,9 +1799,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
-        <v>10110</v>
+        <v>1060</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1821,7 +1827,7 @@
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>10120</v>
+        <v>1070</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1845,9 +1851,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:8">
+    <row r="25" spans="1:8">
       <c r="A25">
-        <v>10130</v>
+        <v>10110</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1873,7 +1879,7 @@
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10210</v>
+        <v>10120</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1899,7 +1905,7 @@
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10220</v>
+        <v>10130</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1925,7 +1931,7 @@
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>10230</v>
+        <v>10210</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1951,7 +1957,7 @@
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10310</v>
+        <v>10220</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1977,7 +1983,7 @@
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10320</v>
+        <v>10230</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10330</v>
+        <v>10310</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2029,7 +2035,7 @@
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10410</v>
+        <v>10320</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
@@ -2055,7 +2061,7 @@
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10420</v>
+        <v>10330</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -2081,7 +2087,7 @@
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10430</v>
+        <v>10410</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2107,7 +2113,7 @@
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10510</v>
+        <v>10420</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2133,7 +2139,7 @@
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10520</v>
+        <v>10430</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
@@ -2159,7 +2165,7 @@
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10530</v>
+        <v>10510</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2185,7 +2191,7 @@
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>10610</v>
+        <v>10520</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
@@ -2211,7 +2217,7 @@
     </row>
     <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>10620</v>
+        <v>10530</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -2237,7 +2243,7 @@
     </row>
     <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
-        <v>10630</v>
+        <v>10610</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2263,7 +2269,7 @@
     </row>
     <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
-        <v>10710</v>
+        <v>10620</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -2289,7 +2295,7 @@
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
-        <v>10720</v>
+        <v>10630</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
@@ -2315,7 +2321,7 @@
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
-        <v>10730</v>
+        <v>10710</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -2341,7 +2347,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
-        <v>10810</v>
+        <v>10720</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -2367,7 +2373,7 @@
     </row>
     <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
-        <v>10820</v>
+        <v>10730</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -2393,7 +2399,7 @@
     </row>
     <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
-        <v>10830</v>
+        <v>10810</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
@@ -2419,7 +2425,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
-        <v>10910</v>
+        <v>10820</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -2445,7 +2451,7 @@
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
-        <v>10920</v>
+        <v>10830</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
-        <v>10930</v>
+        <v>10910</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
-        <v>11010</v>
+        <v>10920</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
@@ -2523,7 +2529,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:8">
       <c r="A51">
-        <v>11020</v>
+        <v>10930</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2549,7 +2555,7 @@
     </row>
     <row r="52" customFormat="1" spans="1:8">
       <c r="A52">
-        <v>11030</v>
+        <v>11010</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2575,7 +2581,7 @@
     </row>
     <row r="53" customFormat="1" spans="1:8">
       <c r="A53">
-        <v>12010</v>
+        <v>11020</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
@@ -2601,7 +2607,7 @@
     </row>
     <row r="54" customFormat="1" spans="1:8">
       <c r="A54">
-        <v>12020</v>
+        <v>11030</v>
       </c>
       <c r="B54" t="s">
         <v>60</v>
@@ -2627,7 +2633,7 @@
     </row>
     <row r="55" customFormat="1" spans="1:8">
       <c r="A55">
-        <v>12030</v>
+        <v>12010</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
@@ -2651,9 +2657,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" customFormat="1" spans="1:8">
       <c r="A56">
-        <v>20010</v>
+        <v>12020</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -2679,7 +2685,7 @@
     </row>
     <row r="57" customFormat="1" spans="1:8">
       <c r="A57">
-        <v>20020</v>
+        <v>12030</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
@@ -2705,7 +2711,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>30010</v>
+        <v>20010</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
@@ -2714,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2731,7 +2737,7 @@
     </row>
     <row r="59" customFormat="1" spans="1:8">
       <c r="A59">
-        <v>30011</v>
+        <v>20020</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
@@ -2757,7 +2763,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B60" t="s">
         <v>66</v>
@@ -2766,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2781,9 +2787,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" customFormat="1" spans="1:8">
       <c r="A61">
-        <v>30030</v>
+        <v>30011</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -2809,7 +2815,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>30040</v>
+        <v>30020</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
@@ -2835,7 +2841,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>30050</v>
+        <v>30030</v>
       </c>
       <c r="B63" t="s">
         <v>69</v>
@@ -2861,7 +2867,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>30060</v>
+        <v>30040</v>
       </c>
       <c r="B64" t="s">
         <v>70</v>
@@ -2887,7 +2893,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>30110</v>
+        <v>30050</v>
       </c>
       <c r="B65" t="s">
         <v>71</v>
@@ -2896,18 +2902,70 @@
         <v>0</v>
       </c>
       <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>30060</v>
+      </c>
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>30110</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
         <v>2010</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65">
-        <v>1</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65" t="b">
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2925,7 +2983,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2933,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2941,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2949,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2957,7 +3015,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2965,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2973,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2981,7 +3039,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2989,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2997,7 +3055,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3005,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3013,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3021,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3029,7 +3087,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3037,7 +3095,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
